--- a/ProductBacklog- Nhóm 9.xlsx
+++ b/ProductBacklog- Nhóm 9.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dangd\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D50B73-4ABB-492A-9DC6-7C8AA309FB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D9BD3D-2371-406E-A882-27AC266ADBD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Information" sheetId="7" r:id="rId1"/>
     <sheet name="Team" sheetId="4" r:id="rId2"/>
     <sheet name="Product backlog" sheetId="1" r:id="rId3"/>
     <sheet name="Sprint backlog" sheetId="6" r:id="rId4"/>
+    <sheet name="PERT " sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028" concurrentCalc="0"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="152">
   <si>
     <t>I. Requirements</t>
   </si>
@@ -309,12 +310,204 @@
   <si>
     <t>Tuấn Anh</t>
   </si>
+  <si>
+    <t>Bảng công việc xây dựng web đọc truyện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã </t>
+  </si>
+  <si>
+    <t>Thời gian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Công việc trước </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Công việc </t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B </t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Phân tích yêu cầu &amp; Mô hình hóa</t>
+  </si>
+  <si>
+    <t>Thiết kế UI/UX (Web &amp; Mobile App)</t>
+  </si>
+  <si>
+    <t>Thiết kế cơ sở dữ liệu (Database Design)</t>
+  </si>
+  <si>
+    <t>Lập trình Front-end (Web &amp; Mobile App)</t>
+  </si>
+  <si>
+    <t>Lập trình Back-end RESTful API</t>
+  </si>
+  <si>
+    <t>Tích hợp hệ thống &amp; Payment Gateway</t>
+  </si>
+  <si>
+    <t>Kiểm thử hệ thống (QA/QC &amp; Bug Fix)</t>
+  </si>
+  <si>
+    <t>Triển khai (Deployment), UAT &amp; Nghiệm thu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C </t>
+  </si>
+  <si>
+    <t>D, E</t>
+  </si>
+  <si>
+    <t>6 ngày</t>
+  </si>
+  <si>
+    <t>9 ngày</t>
+  </si>
+  <si>
+    <t>21 ngày</t>
+  </si>
+  <si>
+    <t>24 ngày</t>
+  </si>
+  <si>
+    <t>12 ngày</t>
+  </si>
+  <si>
+    <t>16 ngày</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đường 1: </t>
+  </si>
+  <si>
+    <t>A -&gt; B -&gt; D -&gt; F -&gt; G -&gt; H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thời gian: </t>
+  </si>
+  <si>
+    <t>6 + 9 + 21 + 9 + 12 + 16 = 73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đường 2: </t>
+  </si>
+  <si>
+    <t>Và</t>
+  </si>
+  <si>
+    <t>A -&gt; C -&gt; E -&gt; F -&gt; G -&gt; H</t>
+  </si>
+  <si>
+    <t>6 + 6 + 24 + 9 + 12 + 16 = 73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hai đường đều dài 73 ngày </t>
+  </si>
+  <si>
+    <t>Vậy Project này có hai Critical Paths</t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>20/09/2027</t>
+  </si>
+  <si>
+    <t>20/09/2028</t>
+  </si>
+  <si>
+    <t>20/09/2029</t>
+  </si>
+  <si>
+    <t>20/09/2030</t>
+  </si>
+  <si>
+    <t>20/09/2031</t>
+  </si>
+  <si>
+    <t>01/12/2026</t>
+  </si>
+  <si>
+    <t>Đã hoàn thành UI &amp; CSDL</t>
+  </si>
+  <si>
+    <t>25/10/2026</t>
+  </si>
+  <si>
+    <t>Tìm kiếm theo tên, thể loại</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>Đã nối API chi tiết</t>
+  </si>
+  <si>
+    <t>Xác thực thông tin</t>
+  </si>
+  <si>
+    <t>Sử dụng JWT Token</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>CRUD Truyện &amp; Thể loại</t>
+  </si>
+  <si>
+    <t>Tổng</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
+    <t>04/10/2026</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -357,8 +550,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,8 +602,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -582,6 +801,101 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -590,7 +904,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -624,23 +938,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -648,22 +961,62 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -755,6 +1108,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>160182</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1440180</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>137430</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94814E79-A26B-BFEB-E36C-73E7C536FEF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="1897542"/>
+          <a:ext cx="6553200" cy="1988928"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1088,244 +1490,244 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="39"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="39"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="39"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="39"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="39"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1349,14 +1751,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
@@ -1391,8 +1793,12 @@
       <c r="D4" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="9"/>
+      <c r="E4" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -1407,8 +1813,12 @@
       <c r="D5" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="9"/>
+      <c r="E5" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -1417,14 +1827,18 @@
       <c r="B6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="27" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="9"/>
+      <c r="E6" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -1433,14 +1847,18 @@
       <c r="B7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="27" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="9"/>
+      <c r="E7" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -1455,24 +1873,32 @@
       <c r="D8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="9"/>
+      <c r="E8" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22">
         <v>6</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="22" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="22"/>
+      <c r="E9" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
@@ -1486,6 +1912,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -1530,20 +1957,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="G5" s="31"/>
+      <c r="C5" s="33"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="25" t="s">
         <v>34</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="26">
         <v>2</v>
       </c>
     </row>
@@ -1554,7 +1980,7 @@
       <c r="B7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="26">
         <v>3</v>
       </c>
       <c r="G7" s="24"/>
@@ -1566,7 +1992,7 @@
       <c r="B8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="26">
         <v>2</v>
       </c>
     </row>
@@ -1577,7 +2003,7 @@
       <c r="B9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1588,7 +2014,7 @@
       <c r="B10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="26">
         <v>2</v>
       </c>
     </row>
@@ -1603,11 +2029,11 @@
       <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1616,7 +2042,7 @@
       <c r="B14" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="26">
         <v>2</v>
       </c>
     </row>
@@ -1627,7 +2053,7 @@
       <c r="B15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="26">
         <v>5</v>
       </c>
     </row>
@@ -1638,7 +2064,7 @@
       <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="26">
         <v>5</v>
       </c>
     </row>
@@ -1649,7 +2075,7 @@
       <c r="B17" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1660,7 +2086,7 @@
       <c r="B18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1671,7 +2097,7 @@
       <c r="B19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1682,7 +2108,7 @@
       <c r="B20" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="26">
         <v>2</v>
       </c>
     </row>
@@ -1700,7 +2126,7 @@
       <c r="B22" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1711,7 +2137,7 @@
       <c r="B23" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="26">
         <v>5</v>
       </c>
     </row>
@@ -1722,7 +2148,7 @@
       <c r="B24" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1733,7 +2159,7 @@
       <c r="B25" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1744,7 +2170,7 @@
       <c r="B26" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1755,7 +2181,7 @@
       <c r="B27" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1766,7 +2192,7 @@
       <c r="B28" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1777,14 +2203,14 @@
       <c r="B29" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="32"/>
+      <c r="C30" s="26"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
@@ -1848,27 +2274,27 @@
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
@@ -1882,10 +2308,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
@@ -1919,178 +2345,253 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9">
-        <f>SUM(C7:C11)</f>
-        <v>11</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+    <row r="5" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+    </row>
+    <row r="6" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="51"/>
+    </row>
+    <row r="7" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="48">
         <v>2</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="E7" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" s="48">
+        <v>2</v>
+      </c>
+      <c r="J7" s="48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="45">
         <v>3</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="E8" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="I8" s="45">
+        <v>3</v>
+      </c>
+      <c r="J8" s="45" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="45">
         <v>2</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="E9" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="I9" s="45">
+        <v>2</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="45">
         <v>2</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="E10" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="I10" s="45">
+        <v>2</v>
+      </c>
+      <c r="J10" s="45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="45">
         <v>2</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="E11" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="I11" s="45">
+        <v>2</v>
+      </c>
+      <c r="J11" s="45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="45">
         <v>3</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="E12" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="I12" s="45">
+        <v>3</v>
+      </c>
+      <c r="J12" s="45" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="A13" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="45"/>
+      <c r="C13" s="44">
+        <v>14</v>
+      </c>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="44">
+        <v>14</v>
+      </c>
+      <c r="J13" s="45"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -2107,4 +2608,202 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F58CC48-3DF3-4D01-B237-0BC9A18A869E}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="4" width="29.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/ProductBacklog- Nhóm 9.xlsx
+++ b/ProductBacklog- Nhóm 9.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dangd\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/456b0bd444409d08/Máy tính/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D9BD3D-2371-406E-A882-27AC266ADBD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{43D9BD3D-2371-406E-A882-27AC266ADBD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1C23617-C4CB-44DF-9AAD-FCB7AE46D627}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Information" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="149">
   <si>
     <t>I. Requirements</t>
   </si>
@@ -267,29 +267,12 @@
     <t>Thống kê doanh thu</t>
   </si>
   <si>
-    <t xml:space="preserve">I. Project Overview (Tổng quan dự án)
-Project Name: Hệ thống Quản lý Đọc truyện (Comic Management System)
-Course: Công nghệ phần mềm nâng cao
-Architecture: Client - Server (Backend RESTful API, Frontend Web App &amp; Mobile App)
-II. Requirements &amp; Scope (Yêu cầu &amp; Phạm vi hệ thống)
-1. Quản lý Nội dung: Quản lý danh mục truyện, thể loại, tác giả, trạng thái phát hành và đăng tải các chương (chapter).
-2. Phân quyền &amp; Truy cập: Thiết lập cơ chế truyện/chương miễn phí, trả phí (bán lẻ từng bộ hoặc đăng ký gói đọc theo tháng).
-3. Trải nghiệm Độc giả: Tìm kiếm, xem chi tiết, đọc truyện, lưu tiến độ đọc, theo dõi truyện yêu thích, thảo luận theo chương.
-4. Quản trị &amp; Báo cáo: Kiểm duyệt bình luận, quản lý tài khoản thành viên, thống kê lượt đọc và thống kê doanh thu.                        III. Deliverables (Sản phẩm nộp)                                                                                                                                               • Sheet Team: Cấu trúc nhân sự nhóm và vai trò                                                                                                                        • Sheet Product backlog: Danh sách User Stories chi tiết theo các Actor                                                                                           • Sheet Sprint backlog: Phân chia công việc triển khai theo từng Sprint  </t>
-  </si>
-  <si>
     <t>Dev</t>
   </si>
   <si>
     <t>Product Owner</t>
   </si>
   <si>
-    <t>Team Lead / Dev</t>
-  </si>
-  <si>
-    <t>ScrumMaster / Dev</t>
-  </si>
-  <si>
     <t>Quản lý truyện và thể loại</t>
   </si>
   <si>
@@ -380,24 +363,6 @@
     <t>D, E</t>
   </si>
   <si>
-    <t>6 ngày</t>
-  </si>
-  <si>
-    <t>9 ngày</t>
-  </si>
-  <si>
-    <t>21 ngày</t>
-  </si>
-  <si>
-    <t>24 ngày</t>
-  </si>
-  <si>
-    <t>12 ngày</t>
-  </si>
-  <si>
-    <t>16 ngày</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -410,9 +375,6 @@
     <t xml:space="preserve">Thời gian: </t>
   </si>
   <si>
-    <t>6 + 9 + 21 + 9 + 12 + 16 = 73</t>
-  </si>
-  <si>
     <t xml:space="preserve">Đường 2: </t>
   </si>
   <si>
@@ -422,51 +384,18 @@
     <t>A -&gt; C -&gt; E -&gt; F -&gt; G -&gt; H</t>
   </si>
   <si>
-    <t>6 + 6 + 24 + 9 + 12 + 16 = 73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hai đường đều dài 73 ngày </t>
-  </si>
-  <si>
     <t>Vậy Project này có hai Critical Paths</t>
   </si>
   <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
-    <t>20/09/2027</t>
-  </si>
-  <si>
-    <t>20/09/2028</t>
-  </si>
-  <si>
-    <t>20/09/2029</t>
-  </si>
-  <si>
-    <t>20/09/2030</t>
-  </si>
-  <si>
-    <t>20/09/2031</t>
-  </si>
-  <si>
     <t>01/12/2026</t>
   </si>
   <si>
     <t>Đã hoàn thành UI &amp; CSDL</t>
   </si>
   <si>
-    <t>25/10/2026</t>
-  </si>
-  <si>
     <t>Tìm kiếm theo tên, thể loại</t>
   </si>
   <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
     <t>Đã nối API chi tiết</t>
   </si>
   <si>
@@ -476,31 +405,191 @@
     <t>Sử dụng JWT Token</t>
   </si>
   <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>14/10/2026</t>
-  </si>
-  <si>
     <t>CRUD Truyện &amp; Thể loại</t>
   </si>
   <si>
     <t>Tổng</t>
   </si>
   <si>
-    <t>05/10/2026</t>
-  </si>
-  <si>
-    <t>04/10/2026</t>
-  </si>
-  <si>
-    <t>06/10/2026</t>
-  </si>
-  <si>
-    <t>08/10/2026</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
+    <t>5 ngày</t>
+  </si>
+  <si>
+    <t>8 ngày</t>
+  </si>
+  <si>
+    <t>19 ngày</t>
+  </si>
+  <si>
+    <t>22 ngày</t>
+  </si>
+  <si>
+    <t>11 ngày</t>
+  </si>
+  <si>
+    <t>14 ngày</t>
+  </si>
+  <si>
+    <t>5 + 8 + 19 + 8 + 11 + 14 = 65 ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hai đường đều dài 65 ngày </t>
+  </si>
+  <si>
+    <t>5 + 5 + 22 + 8 + 11 + 14 = 65 ngày</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ScrumMaster/ Dev</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Team Lead / Dev</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sheet Team:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Cấu trúc nhân sự nhóm và vai trò (PO, Scrum Master, Lead, Dev, Tester)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sheet Product backlog:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Danh sách User Stories chi tiết theo các Actor kèm Story Points</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sheet Sprint backlog:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Phân chia User Stories vào từng Sprint phát triển cụ thể</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Tên dự án:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Hệ thống Quản lý Đọc truyện (Comic Management System)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Môn học:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Công nghệ phần mềm nâng cao</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Kiến trúc hệ thống:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Client - Server (Backend RESTful API kết nối Web App &amp; Mobile App)</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Luồng nghiệp vụ chính:</t>
+  </si>
+  <si>
+    <t>• Quản lý Nội dung: Tạo/chỉnh sửa bộ truyện, phân loại thể loại, đăng tải/lên lịch phát hành các chương (chapter).</t>
+  </si>
+  <si>
+    <t>• Phân quyền &amp; Giá cước: Đặt trạng thái Truyện/Chương miễn phí hoặc trả phí; thiết lập mua lẻ từng truyện hoặc gói đọc theo tháng.</t>
+  </si>
+  <si>
+    <t>• Trải nghiệm Độc giả: Tìm kiếm, duyệt danh mục, đọc chương, lưu tiến độ đọc, đánh giá/bình luận theo chương, theo dõi truyện yêu thích.</t>
+  </si>
+  <si>
+    <t>• Quản trị &amp; Báo cáo: Kiểm duyệt bình luận/spam, quản lý tài khoản thành viên, thống kê lượt đọc và báo cáo doanh thu chi tiết.</t>
+  </si>
+  <si>
+    <t>II. Deliverables (Sản phẩm bàn giao trong file)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sheet PERT:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Sơ đồ/Bảng ước tính thời gian thực hiện các tác vụ theo mô hình PERT</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -615,7 +704,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -896,6 +985,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -904,7 +1008,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -943,17 +1047,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -970,37 +1082,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1011,11 +1097,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1115,22 +1208,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>160182</xdr:rowOff>
+      <xdr:rowOff>47123</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1440180</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>137430</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>67924</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94814E79-A26B-BFEB-E36C-73E7C536FEF0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D82A03F-E3B3-9ED4-7DC0-369DEB5E67A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1146,8 +1239,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="228600" y="1897542"/>
-          <a:ext cx="6553200" cy="1988928"/>
+          <a:off x="0" y="1813170"/>
+          <a:ext cx="7876839" cy="2405413"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1157,6 +1250,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1490,249 +1587,270 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="A3" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
+      <c r="A4" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
+      <c r="A5" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
+      <c r="A6" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
+      <c r="A7" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="31"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
+      <c r="A8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
+      <c r="A9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="50"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
+      <c r="A10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
+      <c r="A11" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="50"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="31"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
+      <c r="A12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
+      <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
+      <c r="A15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
+      <c r="A16" s="50"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="50"/>
+      <c r="L16" s="50"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
+      <c r="A17" s="50"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50"/>
+      <c r="L17" s="50"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
+      <c r="A18" s="50"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="50"/>
+      <c r="L18" s="50"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
+      <c r="A19" s="50"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:L19"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1751,14 +1869,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
@@ -1791,13 +1909,13 @@
         <v>32</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1811,13 +1929,13 @@
         <v>31</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1831,13 +1949,13 @@
         <v>25</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1851,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1871,13 +1989,13 @@
         <v>28</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1891,13 +2009,13 @@
         <v>30</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="42" t="s">
-        <v>134</v>
+      <c r="F9" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1957,10 +2075,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="33"/>
+      <c r="C5" s="37"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -2029,11 +2147,11 @@
       <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2113,11 +2231,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -2274,27 +2392,27 @@
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
     <col min="8" max="8" width="11.88671875" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
@@ -2308,10 +2426,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
@@ -2346,252 +2464,252 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="51"/>
-    </row>
-    <row r="7" spans="1:10" ht="66" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="47">
         <v>2</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="49">
+        <v>46152</v>
+      </c>
+      <c r="G7" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="49">
+        <v>46122</v>
+      </c>
+      <c r="I7" s="47">
+        <v>2</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="47">
+        <v>3</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="49">
+        <v>46091</v>
+      </c>
+      <c r="F8" s="49">
+        <v>46305</v>
+      </c>
+      <c r="G8" s="49">
+        <v>46063</v>
+      </c>
+      <c r="H8" s="49">
+        <v>46305</v>
+      </c>
+      <c r="I8" s="47">
+        <v>3</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="47">
+        <v>2</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="49">
+        <v>46091</v>
+      </c>
+      <c r="F9" s="49">
+        <v>46275</v>
+      </c>
+      <c r="G9" s="49">
+        <v>46091</v>
+      </c>
+      <c r="H9" s="49">
+        <v>46275</v>
+      </c>
+      <c r="I9" s="47">
+        <v>2</v>
+      </c>
+      <c r="J9" s="47" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="47">
+        <v>2</v>
+      </c>
+      <c r="D10" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="F7" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="G7" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="I7" s="48">
+      <c r="E10" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10" s="49">
+        <v>46122</v>
+      </c>
+      <c r="G10" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="H10" s="49">
+        <v>46122</v>
+      </c>
+      <c r="I10" s="47">
         <v>2</v>
       </c>
-      <c r="J7" s="48" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="45">
+      <c r="J10" s="47" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="47">
+        <v>2</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="49">
+        <v>46152</v>
+      </c>
+      <c r="G11" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="49">
+        <v>46152</v>
+      </c>
+      <c r="I11" s="47">
+        <v>2</v>
+      </c>
+      <c r="J11" s="47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="47">
         <v>3</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D12" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="H8" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="I8" s="45">
+      <c r="E12" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="49">
+        <v>46336</v>
+      </c>
+      <c r="G12" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="H12" s="49">
+        <v>46305</v>
+      </c>
+      <c r="I12" s="47">
         <v>3</v>
       </c>
-      <c r="J8" s="45" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="66" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="45">
-        <v>2</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="G9" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="H9" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="45">
-        <v>2</v>
-      </c>
-      <c r="J9" s="45" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="45">
-        <v>2</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="F10" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="G10" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="H10" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="I10" s="45">
-        <v>2</v>
-      </c>
-      <c r="J10" s="45" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="45">
-        <v>2</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="G11" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="H11" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="I11" s="45">
-        <v>2</v>
-      </c>
-      <c r="J11" s="45" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="45">
-        <v>3</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="H12" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="I12" s="45">
-        <v>3</v>
-      </c>
-      <c r="J12" s="45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="44">
+      <c r="J12" s="47" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="47"/>
+      <c r="C13" s="48">
         <v>14</v>
       </c>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="44">
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="48">
         <v>14</v>
       </c>
-      <c r="J13" s="45"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -2622,181 +2740,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="34"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="38" t="s">
+      <c r="D2" s="29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="B5" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="38" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="D6" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="C7" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B8" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="C8" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="C9" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B10" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>99</v>
+      <c r="C10" s="28" t="s">
+        <v>96</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/ProductBacklog- Nhóm 9.xlsx
+++ b/ProductBacklog- Nhóm 9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/456b0bd444409d08/Máy tính/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{43D9BD3D-2371-406E-A882-27AC266ADBD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1C23617-C4CB-44DF-9AAD-FCB7AE46D627}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{43D9BD3D-2371-406E-A882-27AC266ADBD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A334858-3560-45AB-A2EA-4E3D4411385F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="148">
   <si>
     <t>I. Requirements</t>
   </si>
@@ -268,9 +268,6 @@
   </si>
   <si>
     <t>Dev</t>
-  </si>
-  <si>
-    <t>Product Owner</t>
   </si>
   <si>
     <t>Quản lý truyện và thể loại</t>
@@ -1008,7 +1005,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1055,16 +1052,34 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1082,33 +1097,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1588,267 +1584,267 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
+        <v>138</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
+        <v>139</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
+        <v>140</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
+        <v>143</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>145</v>
-      </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
+        <v>144</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
+        <v>145</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
+        <v>146</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
+        <v>135</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
+        <v>136</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
+        <v>137</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
+        <v>147</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="50"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="50"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="50"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1869,14 +1865,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
@@ -1909,13 +1905,13 @@
         <v>32</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1929,13 +1925,13 @@
         <v>31</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1952,10 +1948,10 @@
         <v>76</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1969,13 +1965,13 @@
         <v>24</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1992,10 +1988,10 @@
         <v>76</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2012,10 +2008,10 @@
         <v>76</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2075,10 +2071,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="37"/>
+      <c r="C5" s="43"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -2147,11 +2143,11 @@
       <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2231,11 +2227,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="46"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -2401,18 +2397,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
@@ -2426,10 +2422,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
@@ -2476,240 +2472,240 @@
       <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="45"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="32">
         <v>2</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="34">
+        <v>46152</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="H7" s="34">
+        <v>46122</v>
+      </c>
+      <c r="I7" s="32">
+        <v>2</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="32">
+        <v>3</v>
+      </c>
+      <c r="D8" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="F7" s="49">
+      <c r="E8" s="34">
+        <v>46091</v>
+      </c>
+      <c r="F8" s="34">
+        <v>46305</v>
+      </c>
+      <c r="G8" s="34">
+        <v>46063</v>
+      </c>
+      <c r="H8" s="34">
+        <v>46305</v>
+      </c>
+      <c r="I8" s="32">
+        <v>3</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="32">
+        <v>2</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="34">
+        <v>46091</v>
+      </c>
+      <c r="F9" s="34">
+        <v>46275</v>
+      </c>
+      <c r="G9" s="34">
+        <v>46091</v>
+      </c>
+      <c r="H9" s="34">
+        <v>46275</v>
+      </c>
+      <c r="I9" s="32">
+        <v>2</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="32">
+        <v>2</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="34">
+        <v>46122</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="H10" s="34">
+        <v>46122</v>
+      </c>
+      <c r="I10" s="32">
+        <v>2</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="32">
+        <v>2</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="34">
         <v>46152</v>
       </c>
-      <c r="G7" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="H7" s="49">
-        <v>46122</v>
-      </c>
-      <c r="I7" s="47">
+      <c r="G11" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" s="34">
+        <v>46152</v>
+      </c>
+      <c r="I11" s="32">
         <v>2</v>
       </c>
-      <c r="J7" s="47" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="47">
+      <c r="J11" s="32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="32">
         <v>3</v>
       </c>
-      <c r="D8" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="49">
-        <v>46091</v>
-      </c>
-      <c r="F8" s="49">
+      <c r="D12" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="34">
+        <v>46336</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="34">
         <v>46305</v>
       </c>
-      <c r="G8" s="49">
-        <v>46063</v>
-      </c>
-      <c r="H8" s="49">
-        <v>46305</v>
-      </c>
-      <c r="I8" s="47">
+      <c r="I12" s="32">
         <v>3</v>
       </c>
-      <c r="J8" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="47">
-        <v>2</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="49">
-        <v>46091</v>
-      </c>
-      <c r="F9" s="49">
-        <v>46275</v>
-      </c>
-      <c r="G9" s="49">
-        <v>46091</v>
-      </c>
-      <c r="H9" s="49">
-        <v>46275</v>
-      </c>
-      <c r="I9" s="47">
-        <v>2</v>
-      </c>
-      <c r="J9" s="47" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="47">
-        <v>2</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" s="49">
-        <v>46122</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="H10" s="49">
-        <v>46122</v>
-      </c>
-      <c r="I10" s="47">
-        <v>2</v>
-      </c>
-      <c r="J10" s="47" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="47">
-        <v>2</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="49">
-        <v>46152</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" s="49">
-        <v>46152</v>
-      </c>
-      <c r="I11" s="47">
-        <v>2</v>
-      </c>
-      <c r="J11" s="47" t="s">
+      <c r="J12" s="32" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="47">
-        <v>3</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12" s="49">
-        <v>46336</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="H12" s="49">
-        <v>46305</v>
-      </c>
-      <c r="I12" s="47">
-        <v>3</v>
-      </c>
-      <c r="J12" s="47" t="s">
+    <row r="13" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="33" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="48">
+      <c r="B13" s="32"/>
+      <c r="C13" s="33">
         <v>14</v>
       </c>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="48">
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33">
         <v>14</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="32"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -2740,181 +2736,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="34"/>
+      <c r="A1" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="29" t="s">
         <v>86</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>125</v>
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
         <v>109</v>
-      </c>
-      <c r="B26" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
